--- a/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -401,7 +401,7 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>PractitionerRole.meta.versionId</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4893" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4895" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -490,7 +490,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role-exercice</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -865,11 +865,10 @@
     <t>PractitionerRole.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value | Namespace du RASS)</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.
-Namespace du RASS)</t>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -942,7 +941,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -974,6 +981,10 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -5616,7 +5627,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>119</v>
@@ -5628,7 +5639,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5735,7 +5746,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -5854,7 +5865,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5973,7 +5984,7 @@
         <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -6090,7 +6101,7 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -6147,7 +6158,9 @@
       <c r="M33" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6196,7 +6209,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6205,22 +6218,22 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6228,10 +6241,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6254,16 +6267,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6313,7 +6326,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6322,22 +6335,22 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6345,13 +6358,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>230</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6376,7 +6389,7 @@
         <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>233</v>
@@ -6447,7 +6460,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>237</v>
@@ -6464,7 +6477,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>245</v>
@@ -6579,7 +6592,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -6673,7 +6686,7 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>119</v>
@@ -6685,7 +6698,7 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6696,7 +6709,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>249</v>
@@ -6792,7 +6805,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -6815,7 +6828,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>260</v>
@@ -6911,7 +6924,7 @@
         <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
@@ -6934,7 +6947,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>271</v>
@@ -6982,7 +6995,7 @@
         <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>277</v>
@@ -7030,7 +7043,7 @@
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
@@ -7053,7 +7066,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>283</v>
@@ -7147,7 +7160,7 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -7170,7 +7183,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>293</v>
@@ -7204,7 +7217,9 @@
       <c r="M42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N42" s="2"/>
+      <c r="N42" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7253,7 +7268,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7262,22 +7277,22 @@
         <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7285,10 +7300,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7311,16 +7326,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7370,7 +7385,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7379,22 +7394,22 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7402,10 +7417,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7428,70 +7443,70 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q44" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="R44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7509,24 +7524,24 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7552,14 +7567,14 @@
         <v>294</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7608,7 +7623,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7626,24 +7641,24 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7755,10 +7770,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7872,10 +7887,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7898,16 +7913,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7957,7 +7972,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7966,19 +7981,19 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7989,10 +8004,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8015,23 +8030,23 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>78</v>
@@ -8076,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8085,19 +8100,19 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -8108,10 +8123,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8134,13 +8149,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8191,7 +8206,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8212,7 +8227,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -8223,10 +8238,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8249,13 +8264,13 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8306,7 +8321,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8327,7 +8342,7 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8338,10 +8353,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8367,16 +8382,16 @@
         <v>261</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8405,13 +8420,13 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8421,7 +8436,7 @@
         <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8439,13 +8454,13 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8453,13 +8468,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
@@ -8484,16 +8499,16 @@
         <v>261</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8522,7 +8537,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8540,7 +8555,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8555,16 +8570,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8572,13 +8587,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8603,16 +8618,16 @@
         <v>261</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8641,7 +8656,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8659,7 +8674,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8674,16 +8689,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8691,13 +8706,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8722,16 +8737,16 @@
         <v>261</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8760,7 +8775,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8778,7 +8793,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8793,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8810,13 +8825,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8841,16 +8856,16 @@
         <v>261</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8879,7 +8894,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8897,7 +8912,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8912,16 +8927,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8929,13 +8944,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
@@ -8960,16 +8975,16 @@
         <v>261</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8998,7 +9013,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -9016,7 +9031,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9031,16 +9046,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -9048,13 +9063,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
@@ -9079,16 +9094,16 @@
         <v>261</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9117,7 +9132,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9135,7 +9150,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9150,16 +9165,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9167,13 +9182,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -9198,16 +9213,16 @@
         <v>261</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9236,7 +9251,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9254,7 +9269,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9269,16 +9284,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9286,10 +9301,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9315,10 +9330,10 @@
         <v>261</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9349,25 +9364,25 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9385,13 +9400,13 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9399,10 +9414,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9425,13 +9440,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9482,7 +9497,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9503,21 +9518,21 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9540,13 +9555,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9597,7 +9612,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9615,10 +9630,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9629,10 +9644,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9655,17 +9670,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9702,17 +9717,17 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9724,19 +9739,19 @@
         <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9744,13 +9759,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9772,17 +9787,17 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9831,7 +9846,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9843,19 +9858,19 @@
         <v>209</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9863,10 +9878,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,10 +9993,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10095,13 +10110,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
@@ -10123,13 +10138,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10212,10 +10227,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10327,10 +10342,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10442,10 +10457,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10471,13 +10486,13 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10485,7 +10500,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -10527,7 +10542,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>90</v>
@@ -10559,10 +10574,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10588,10 +10603,10 @@
         <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10603,7 +10618,7 @@
         <v>78</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>78</v>
@@ -10622,7 +10637,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10640,7 +10655,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10672,13 +10687,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
@@ -10700,13 +10715,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10789,10 +10804,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10904,10 +10919,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11021,13 +11036,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>78</v>
@@ -11052,7 +11067,7 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>202</v>
@@ -11138,10 +11153,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11253,10 +11268,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11368,10 +11383,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11397,13 +11412,13 @@
         <v>137</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11411,7 +11426,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>78</v>
@@ -11453,7 +11468,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>90</v>
@@ -11485,10 +11500,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11514,10 +11529,10 @@
         <v>261</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11548,7 +11563,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11566,7 +11581,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11598,13 +11613,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>78</v>
@@ -11629,7 +11644,7 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>202</v>
@@ -11715,10 +11730,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11830,10 +11845,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11945,10 +11960,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11974,13 +11989,13 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11988,7 +12003,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>78</v>
@@ -12030,7 +12045,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>90</v>
@@ -12062,10 +12077,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12091,10 +12106,10 @@
         <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12145,7 +12160,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12177,13 +12192,13 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>78</v>
@@ -12294,10 +12309,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12409,10 +12424,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12524,10 +12539,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12553,13 +12568,13 @@
         <v>137</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12567,7 +12582,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>78</v>
@@ -12609,7 +12624,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>90</v>
@@ -12641,10 +12656,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12670,10 +12685,10 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12724,7 +12739,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12756,13 +12771,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12787,7 +12802,7 @@
         <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>202</v>
@@ -12873,10 +12888,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12988,10 +13003,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13103,10 +13118,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13132,13 +13147,13 @@
         <v>137</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13146,7 +13161,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>78</v>
@@ -13188,7 +13203,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>90</v>
@@ -13220,10 +13235,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13249,10 +13264,10 @@
         <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13303,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13335,13 +13350,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>78</v>
@@ -13452,10 +13467,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13567,10 +13582,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13682,10 +13697,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13711,13 +13726,13 @@
         <v>137</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13725,7 +13740,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>78</v>
@@ -13767,7 +13782,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>90</v>
@@ -13799,10 +13814,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13828,10 +13843,10 @@
         <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13882,7 +13897,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13914,13 +13929,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>78</v>
@@ -13945,7 +13960,7 @@
         <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>202</v>
@@ -14031,10 +14046,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14146,10 +14161,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14261,10 +14276,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14290,13 +14305,13 @@
         <v>137</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14304,7 +14319,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>78</v>
@@ -14346,7 +14361,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14378,10 +14393,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14404,13 +14419,13 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14461,7 +14476,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14493,13 +14508,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>78</v>
@@ -14524,7 +14539,7 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>202</v>
@@ -14610,10 +14625,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14725,10 +14740,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14840,10 +14855,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14869,13 +14884,13 @@
         <v>137</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14883,7 +14898,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -14925,7 +14940,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>90</v>
@@ -14957,10 +14972,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14983,13 +14998,13 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15040,7 +15055,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15072,10 +15087,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15101,13 +15116,13 @@
         <v>137</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15115,7 +15130,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>78</v>
@@ -15157,7 +15172,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>90</v>
@@ -15189,10 +15204,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15215,13 +15230,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15272,7 +15287,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15304,10 +15319,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15333,10 +15348,10 @@
         <v>176</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15348,7 +15363,7 @@
         <v>78</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>78</v>
@@ -15366,10 +15381,10 @@
         <v>254</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15387,7 +15402,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15396,7 +15411,7 @@
         <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>102</v>
@@ -15405,13 +15420,13 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>78</v>
@@ -15419,10 +15434,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15448,16 +15463,16 @@
         <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15506,7 +15521,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15524,10 +15539,10 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>291</v>
@@ -15538,10 +15553,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15567,16 +15582,16 @@
         <v>176</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15604,10 +15619,10 @@
         <v>254</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15625,7 +15640,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15643,13 +15658,13 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>78</v>
@@ -15657,10 +15672,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15683,16 +15698,16 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15742,7 +15757,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15774,10 +15789,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15803,10 +15818,10 @@
         <v>294</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15857,7 +15872,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15878,10 +15893,10 @@
         <v>199</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>78</v>
@@ -15889,10 +15904,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15915,16 +15930,16 @@
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15974,7 +15989,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15995,7 +16010,7 @@
         <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -16006,10 +16021,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16121,10 +16136,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16238,14 +16253,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16267,10 +16282,10 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
@@ -16325,7 +16340,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16357,10 +16372,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16386,10 +16401,10 @@
         <v>176</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16419,28 +16434,28 @@
         <v>254</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16461,7 +16476,7 @@
         <v>78</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -16472,10 +16487,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16498,13 +16513,13 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16555,7 +16570,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16576,7 +16591,7 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -16587,10 +16602,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16613,16 +16628,16 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16672,7 +16687,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16693,7 +16708,7 @@
         <v>78</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -16704,10 +16719,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16730,16 +16745,16 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M124" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16789,7 +16804,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16810,7 +16825,7 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -16821,10 +16836,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16847,13 +16862,13 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16904,7 +16919,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16925,7 +16940,7 @@
         <v>78</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>78</v>
@@ -16936,10 +16951,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17051,10 +17066,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17168,14 +17183,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17197,10 +17212,10 @@
         <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>114</v>
@@ -17255,7 +17270,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17287,10 +17302,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17316,10 +17331,10 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17370,7 +17385,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>90</v>
@@ -17402,10 +17417,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17431,10 +17446,10 @@
         <v>294</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17485,7 +17500,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17506,7 +17521,7 @@
         <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17517,10 +17532,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17546,10 +17561,10 @@
         <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17600,7 +17615,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17621,7 +17636,7 @@
         <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -17632,10 +17647,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17658,17 +17673,17 @@
         <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17717,7 +17732,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
